--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20232.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
   <si>
     <t>Mat</t>
   </si>
@@ -71,6 +71,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>JUSTIN GIOVANNI</t>
   </si>
 </sst>
 </file>
@@ -588,16 +597,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>87.09999999999999</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -611,16 +623,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>83.87</v>
+      </c>
+      <c r="H3">
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -634,16 +649,19 @@
         <v>23</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>78.26000000000001</v>
+      </c>
+      <c r="H4">
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -699,13 +717,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>83.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H2">
         <v>7.1</v>
@@ -725,13 +743,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>87.09999999999999</v>
+        <v>83.87</v>
       </c>
       <c r="H3">
         <v>7.2</v>
@@ -751,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>65.22</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="H4">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -770,7 +788,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -800,6 +818,29 @@
         <v>17</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920308</v>
+      </c>
+      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20232.xlsx
+++ b/docentes/De Jesús Orduña Sofía del Pilar - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>Mat</t>
   </si>
@@ -71,15 +71,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>JUSTIN GIOVANNI</t>
   </si>
 </sst>
 </file>
@@ -717,16 +708,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>87.09999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -743,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>83.87</v>
+        <v>96.77</v>
       </c>
       <c r="H3">
         <v>7.2</v>
@@ -769,16 +760,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>78.26000000000001</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -788,7 +779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -818,29 +809,6 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920308</v>
-      </c>
-      <c r="B2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
